--- a/apps/reclaim-protocol/Cool_Hollow_Coaching_Milestone_1_Reclaim_Protocol_Template.xlsx
+++ b/apps/reclaim-protocol/Cool_Hollow_Coaching_Milestone_1_Reclaim_Protocol_Template.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Time Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Examples" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Starter Ideas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Time Log" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,12 +43,32 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005A5A5A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -61,21 +85,8 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="005A5A5A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
       <color rgb="006B6B6B"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -92,12 +103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
+        <fgColor rgb="00E8C766"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8C766"/>
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -132,11 +143,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -144,19 +156,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,10 +541,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001A1A1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -535,125 +558,144 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 1: The 15-Hour Reclaim Protocol</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>How to use this template</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>List every task from your Liberation Audit time log. Mark each one owner_only, delegate, automate, or eliminate, then rate how ready it is to move. The tool ranks everything that isn't owner_only and builds your reclaim plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>List every task from your Liberation Audit time log. Mark each one owner_only, delegate, automate, or eliminate, then rate how ready it is to move. The tool ranks everything that isn't owner_only and builds your reclaim plan. Stuck on where to start? The Starter Ideas tab lists the tasks that eat most owners' weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Three steps: fill in the data tab(s), save this file, then upload this same file into the tool. The Examples and Starter Ideas tabs are for reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads them, only type your real data on the data tab(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>On the "Time Log" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>What to put here</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>One row per task from your one-week time log.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Hours Per Week</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>How many hours a week this task costs you, total.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>owner_only (only you can do it today), delegate, automate, or eliminate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>owner_only (only you can do it today), delegate, automate, or eliminate. Pick from the dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Documented</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>yes or no. Is there a written process for this task?</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Trained Replacement</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>yes or no. Is there already someone trained to take this on?</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>low, medium, or high. What happens if this gets handed off and something goes wrong?</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Fill in the data tab, save the file, then upload it straight into the tool.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -662,10 +704,417 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B6B6B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 1: The 15-Hour Reclaim Protocol</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Filled-in examples, for reference only. Type your own data on the data tab(s), not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, anything you type here is ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Example for the "Time Log" tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Hours Per Week</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Documented</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Trained Replacement</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Approve every invoice before it's paid</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>delegate</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Respond to every support email personally</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>delegate</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Set next quarter's pricing strategy</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>owner_only</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E8C766"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cool Hollow Coaching · Business Without You</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Milestone 1: The 15-Hour Reclaim Protocol</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>The most common answers we see across owner-run businesses. Copy any that are true for yours onto the data tab, reworded to match how your business actually runs, then fill in the numbers and ratings yourself, honestly. Don't copy anything that isn't real for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>The tool never reads this tab, copy items onto the data tab to use them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Money tasks owners hold onto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Approving every quote or estimate before it goes out</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Approving and paying supplier invoices</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Running payroll</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Chasing overdue customer invoices</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Reconciling bank statements / bookkeeping</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Setting or approving every price</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Day-to-day operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Scheduling jobs, staff, or deliveries</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Ordering materials and supplies</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Final review of every job or deliverable before it ships</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Fixing problems the team escalates instead of solving</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Opening and closing the shop or office</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Customers and people</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Answering customer calls and complaints personally</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Writing customer emails, follow-ups, and proposals</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Sitting in on every new-hire interview</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Training every new employee personally</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Posting on social media</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C8A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -682,411 +1131,393 @@
           <t>Cool Hollow Coaching · Business Without You</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Milestone 1: The 15-Hour Reclaim Protocol</t>
         </is>
       </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Hours Per Week</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Documented</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Trained Replacement</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Approve every invoice before it's paid</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>delegate</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Set next quarter's pricing strategy</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>owner_only</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Your data starts here, replace or delete the example rows above</t>
-        </is>
-      </c>
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="C8:C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: owner_only, delegate, automate, eliminate" type="list">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: owner_only, delegate, automate, eliminate" promptTitle="Pick from the list" prompt="owner_only, delegate, automate, or eliminate" type="list">
       <formula1>"owner_only,delegate,automate,eliminate"</formula1>
     </dataValidation>
-    <dataValidation sqref="D8:D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" type="list">
+    <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" promptTitle="Pick from the list" prompt="Is there a written process?" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="E8:E42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" type="list">
+    <dataValidation sqref="E5:E44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: yes, no" promptTitle="Pick from the list" prompt="Is someone already trained for this?" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="F8:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: low, medium, high" type="list">
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Choose one of: low, medium, high" promptTitle="Pick from the list" prompt="Risk if this gets handed off and something goes wrong" type="list">
       <formula1>"low,medium,high"</formula1>
     </dataValidation>
   </dataValidations>
